--- a/results/Int Task Remove ACC -0.7/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_6_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6153758051256675</v>
+        <v>0.6217824903624363</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6230960324364878</v>
+        <v>0.6217024766343952</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6240901182048192</v>
+        <v>0.6243694678787782</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6329646582755345</v>
+        <v>0.6283090964235261</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6326463991827027</v>
+        <v>0.6317714360967668</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6311740268654572</v>
+        <v>0.629542824305018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6289855217054696</v>
+        <v>0.6255233815677104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6336813897247209</v>
+        <v>0.6302591566832414</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6365860277274505</v>
+        <v>0.6280704519877724</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6401668914766423</v>
+        <v>0.6222996863302233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6408044073397132</v>
+        <v>0.6237720586474687</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6315325921255318</v>
+        <v>0.6254435673751506</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6336017750676425</v>
+        <v>0.625762026003464</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6372227454485957</v>
+        <v>0.6232566584990142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6404065335898029</v>
+        <v>0.6232566584990142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6303395694822453</v>
+        <v>0.6213459067291346</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6340399549847954</v>
+        <v>0.6193164313478223</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6437890590704839</v>
+        <v>0.6194756606619789</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6414014175000599</v>
+        <v>0.6235743189854019</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6380601958640285</v>
+        <v>0.6206686833052654</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6373839701175663</v>
+        <v>0.618996975042102</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6358718902395224</v>
+        <v>0.5995773838503963</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6289075033322425</v>
+        <v>0.6126309950435387</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6135460647612359</v>
+        <v>0.6122734274608711</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6018848121572978</v>
+        <v>0.6113970676265653</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6094067011996073</v>
+        <v>0.6152570815142349</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6124312600266579</v>
+        <v>0.5971897422799722</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6133483250991691</v>
+        <v>0.5956377553056484</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6099256929867269</v>
+        <v>0.592892147081594</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6157758737658731</v>
+        <v>0.6087310740595893</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6180441931184203</v>
+        <v>0.6064224485397993</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6150591423166868</v>
+        <v>0.6098095633365526</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.611758226847898</v>
+        <v>0.6036818287027799</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6009735336137472</v>
+        <v>0.5947699754970429</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5957598710202648</v>
+        <v>0.6045202767956198</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6464207325346594</v>
+        <v>0.6359973980573226</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6464207325346594</v>
+        <v>0.6364351789035126</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6244951752320598</v>
+        <v>0.6508400443766911</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6286728496061169</v>
+        <v>0.6480545290563569</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6264448364208124</v>
+        <v>0.6470586474686929</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6317768235547645</v>
+        <v>0.6711731090022428</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6329307372436966</v>
+        <v>0.6726853884157681</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6329307372436966</v>
+        <v>0.6726853884157681</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6036052070779225</v>
+        <v>0.6712527236593211</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6196819803497458</v>
+        <v>0.6675527372277339</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6194034288177124</v>
+        <v>0.6693068536447151</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6239789769416798</v>
+        <v>0.6693068536447151</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6183666424563616</v>
+        <v>0.669863956708782</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6122377106097006</v>
+        <v>0.6660436503819109</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6164161831256834</v>
+        <v>0.667079638601336</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6125557701670511</v>
+        <v>0.6657257903600418</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5836269165382988</v>
+        <v>0.6583250193549417</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5836269165382988</v>
+        <v>0.6542698597664637</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5836269165382988</v>
+        <v>0.5758019330997438</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5803234071082519</v>
+        <v>0.5680032883447335</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5616596563200869</v>
+        <v>0.5737734553958385</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5460994804096064</v>
+        <v>0.5438890263466649</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5440294993255701</v>
+        <v>0.5438890263466649</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5195963796282255</v>
+        <v>0.5338224613100702</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5222214684215147</v>
+        <v>0.5487445227510356</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5223806977356713</v>
+        <v>0.5362097038095314</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5129909570519829</v>
+        <v>0.5261030321411754</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4508775570471941</v>
+        <v>0.5268989791764771</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4657221987213767</v>
+        <v>0.5243920153881763</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4724872496827386</v>
+        <v>0.5225213702500578</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4897578437397738</v>
+        <v>0.5208504601288201</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4700287730164178</v>
+        <v>0.5388367879576346</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4768744363122651</v>
+        <v>0.5077986447550104</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4874230790719206</v>
+        <v>0.5080771962870437</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4852331771635632</v>
+        <v>0.5055704320342244</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5176231732526678</v>
+        <v>0.5010341924000926</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5176231732526678</v>
+        <v>0.5007957474998205</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5176231732526678</v>
+        <v>0.5007957474998205</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5173047146243545</v>
+        <v>0.5001191226823953</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5242691015316343</v>
+        <v>0.4999600929037201</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5239109353425226</v>
+        <v>0.4999600929037201</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5514845439816108</v>
+        <v>0.4998008635895635</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5514845439816108</v>
+        <v>0.4991641458684183</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5444439345204364</v>
+        <v>0.4988059796793066</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5445211547517379</v>
+        <v>0.5006365181856638</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5456349618089089</v>
+        <v>0.500517195967787</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5304367432616868</v>
+        <v>0.5005571030640669</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5293502725654676</v>
+        <v>0.5002785515320334</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.512240903177403</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4883614944409415</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4672685987022213</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4918635416749806</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5085099887461988</v>
+        <v>0.5002785515320334</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4985619477855552</v>
+        <v>0.5002785515320334</v>
       </c>
     </row>
   </sheetData>
